--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -590,12 +591,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -645,12 +646,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_RENT</t>
+          <t>MANICURE_SOLO</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -700,12 +701,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -755,12 +756,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -810,12 +811,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -890,6 +891,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -945,12 +947,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -983,12 +985,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1021,12 +1023,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1059,12 +1061,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1129,6 +1131,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1179,12 +1182,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1220,12 +1223,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1257,12 +1260,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1294,12 +1297,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1366,6 +1369,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1465,6 +1469,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1779,6 +1784,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1946,6 +1952,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2026,12 +2033,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2085,12 +2092,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_RENT</t>
+          <t>MANICURE_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2144,12 +2151,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2203,12 +2210,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2262,12 +2269,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2367,6 +2374,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2487,12 +2495,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2562,12 +2570,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_RENT</t>
+          <t>MANICURE_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2637,12 +2645,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2712,12 +2720,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -2787,12 +2795,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -2898,6 +2906,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2968,12 +2977,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3015,12 +3024,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_RENT</t>
+          <t>MANICURE_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3058,12 +3067,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3101,12 +3110,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3144,12 +3153,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -3223,6 +3232,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3293,12 +3303,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3338,12 +3348,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_RENT</t>
+          <t>MANICURE_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3383,12 +3393,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3428,12 +3438,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3473,12 +3483,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -3551,6 +3561,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3606,12 +3617,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3648,12 +3659,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_RENT</t>
+          <t>MANICURE_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3690,12 +3701,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3732,12 +3743,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3774,12 +3785,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3852,6 +3863,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3922,12 +3934,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3983,12 +3995,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_RENT</t>
+          <t>MANICURE_SOLO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -4044,12 +4056,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -4105,12 +4117,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -4166,12 +4178,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>NAIL_STUDIO</t>
+          <t>MANICURE_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -4258,6 +4270,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4303,12 +4316,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -4337,12 +4350,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -4371,12 +4384,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -4405,12 +4418,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_HOME</t>
+          <t>MANICURE_HOME</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -4466,6 +4479,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4491,12 +4505,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -4513,12 +4527,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -4535,12 +4549,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -4557,12 +4571,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>NAIL_CABINET</t>
+          <t>MANICURE_STANDARD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -502,7 +502,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -891,7 +890,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1131,7 +1129,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1369,7 +1366,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1469,7 +1465,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1779,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1952,7 +1946,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2374,7 +2367,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2543,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0</v>
@@ -2906,7 +2898,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3232,7 +3223,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3561,7 +3551,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3863,7 +3852,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4270,7 +4258,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4479,7 +4466,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -2332,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2483,6 +2483,66 @@
           <t>rampup_start_pct</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>s01</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>s02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>s03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>s04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>s05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>s06</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>s07</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>s08</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>s09</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>s10</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>s11</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>s12</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2558,6 +2618,42 @@
       <c r="W4" s="3" t="n">
         <v>0.45</v>
       </c>
+      <c r="X4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -2633,6 +2729,42 @@
       <c r="W5" s="3" t="n">
         <v>0.45</v>
       </c>
+      <c r="X5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2708,6 +2840,42 @@
       <c r="W6" s="3" t="n">
         <v>0.45</v>
       </c>
+      <c r="X6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2783,6 +2951,42 @@
       <c r="W7" s="3" t="n">
         <v>0.45</v>
       </c>
+      <c r="X7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2857,6 +3061,42 @@
       </c>
       <c r="W8" s="3" t="n">
         <v>0.45</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -2616,7 +2616,7 @@
         <v>3</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="X4" t="n">
         <v>0.8</v>

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -2332,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2543,6 +2543,21 @@
           <t>s12</t>
         </is>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>marketing_min</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>marketing_med</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>marketing_max</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2595,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0</v>
@@ -2653,6 +2668,15 @@
       </c>
       <c r="AI4" t="n">
         <v>1.3</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>70000</v>
       </c>
     </row>
     <row r="5">

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -2332,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AO8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2558,6 +2558,21 @@
           <t>marketing_max</t>
         </is>
       </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>other_opex_min</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>other_opex_med</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>other_opex_max</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2677,6 +2692,15 @@
       </c>
       <c r="AL4" t="n">
         <v>70000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="5">

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -3161,7 +3161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3252,6 +3252,21 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>deposit</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3265,31 +3280,31 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>50000</v>
+        <v>264000</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>330000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>429000</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>150000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>80000</v>
-      </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>10000</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>3</v>
@@ -3298,6 +3313,15 @@
         <is>
           <t>Лампа, фрезер, материалы</t>
         </is>
+      </c>
+      <c r="N4" t="n">
+        <v>30000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="5">

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -578,6 +578,11 @@
           <t>classes_available</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>training_required</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -633,6 +638,9 @@
           <t>Эконом</t>
         </is>
       </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -688,6 +696,9 @@
           <t>Эконом</t>
         </is>
       </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -743,6 +754,9 @@
           <t>Стандарт</t>
         </is>
       </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -798,6 +812,9 @@
           <t>Стандарт|Бизнес</t>
         </is>
       </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -852,6 +869,9 @@
         <is>
           <t>Стандарт|Бизнес</t>
         </is>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -2352,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO8"/>
+  <dimension ref="A1:AO7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>0</v>
@@ -2777,10 +2777,10 @@
         <v>4000</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>0</v>
@@ -2833,6 +2833,24 @@
       <c r="AI5" t="n">
         <v>1.3</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>38500</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>108500</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>13750</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>38750</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2888,10 +2906,10 @@
         <v>7000</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>0</v>
@@ -2944,6 +2962,24 @@
       <c r="AI6" t="n">
         <v>1.3</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>96250</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>175000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>271250</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>124000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2999,10 +3035,10 @@
         <v>15000</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>0</v>
@@ -3055,116 +3091,23 @@
       <c r="AI7" t="n">
         <v>1.3</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>MANICURE_PREMIUM</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>6300</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>11700</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>175000</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>250000</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>375000</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>25000</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>25000</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>12500</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.3</v>
+      <c r="AJ7" t="n">
+        <v>192500</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>350000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>542500</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>99000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>180000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>279000</v>
       </c>
     </row>
   </sheetData>

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -1939,7 +1939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>300000</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>420000</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>540000</v>
@@ -2267,7 +2267,7 @@
         <v>352500</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>493500</v>
+        <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>634500</v>
@@ -2277,65 +2277,6 @@
       </c>
       <c r="O7" s="3" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>MANICURE_PREMIUM</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>премиум</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Мастер × 5, Админ × 2</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Управляющий</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>10ч 6/1</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>500000</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>700000</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>900000</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>587500</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>822500</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>1057500</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2645,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>45000</v>
+        <v>12000</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0</v>
@@ -2705,22 +2646,22 @@
         <v>1.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25000</v>
+        <v>6600</v>
       </c>
       <c r="AK4" t="n">
-        <v>45000</v>
+        <v>12000</v>
       </c>
       <c r="AL4" t="n">
-        <v>70000</v>
+        <v>18600</v>
       </c>
       <c r="AM4" t="n">
-        <v>3000</v>
+        <v>2750</v>
       </c>
       <c r="AN4" t="n">
         <v>5000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8000</v>
+        <v>7750</v>
       </c>
     </row>
     <row r="5">
@@ -2774,7 +2715,7 @@
         <v>4000</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>4000</v>
+        <v>22000</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>0</v>
@@ -2834,22 +2775,22 @@
         <v>1.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38500</v>
+        <v>12100</v>
       </c>
       <c r="AK5" t="n">
-        <v>70000</v>
+        <v>22000</v>
       </c>
       <c r="AL5" t="n">
-        <v>108500</v>
+        <v>34100</v>
       </c>
       <c r="AM5" t="n">
-        <v>13750</v>
+        <v>6325</v>
       </c>
       <c r="AN5" t="n">
-        <v>25000</v>
+        <v>11500</v>
       </c>
       <c r="AO5" t="n">
-        <v>38750</v>
+        <v>17825</v>
       </c>
     </row>
     <row r="6">
@@ -2903,7 +2844,7 @@
         <v>7000</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>7000</v>
+        <v>28000</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>0</v>
@@ -2963,22 +2904,22 @@
         <v>1.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>96250</v>
+        <v>15400</v>
       </c>
       <c r="AK6" t="n">
-        <v>175000</v>
+        <v>28000</v>
       </c>
       <c r="AL6" t="n">
-        <v>271250</v>
+        <v>43400</v>
       </c>
       <c r="AM6" t="n">
-        <v>44000</v>
+        <v>6875</v>
       </c>
       <c r="AN6" t="n">
-        <v>80000</v>
+        <v>12500</v>
       </c>
       <c r="AO6" t="n">
-        <v>124000</v>
+        <v>19375</v>
       </c>
     </row>
     <row r="7">
@@ -3032,7 +2973,7 @@
         <v>15000</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>15000</v>
+        <v>45000</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>0</v>
@@ -3092,22 +3033,22 @@
         <v>1.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>192500</v>
+        <v>24750</v>
       </c>
       <c r="AK7" t="n">
-        <v>350000</v>
+        <v>45000</v>
       </c>
       <c r="AL7" t="n">
-        <v>542500</v>
+        <v>69750</v>
       </c>
       <c r="AM7" t="n">
-        <v>99000</v>
+        <v>9900</v>
       </c>
       <c r="AN7" t="n">
-        <v>180000</v>
+        <v>18000</v>
       </c>
       <c r="AO7" t="n">
-        <v>279000</v>
+        <v>27900</v>
       </c>
     </row>
   </sheetData>

--- a/data/kz/niches/niche_formats_MANICURE.xlsx
+++ b/data/kz/niches/niche_formats_MANICURE.xlsx
@@ -2293,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:AR7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2534,6 +2534,21 @@
           <t>other_opex_max</t>
         </is>
       </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>materials_min</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>materials_med</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>materials_max</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2655,12 +2670,21 @@
         <v>18600</v>
       </c>
       <c r="AM4" t="n">
+        <v>1650</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4650</v>
+      </c>
+      <c r="AP4" t="n">
         <v>2750</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AQ4" t="n">
         <v>5000</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AR4" t="n">
         <v>7750</v>
       </c>
     </row>
@@ -2715,7 +2739,7 @@
         <v>4000</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>0</v>
@@ -2775,22 +2799,31 @@
         <v>1.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12100</v>
+        <v>11000</v>
       </c>
       <c r="AK5" t="n">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="AL5" t="n">
-        <v>34100</v>
+        <v>31000</v>
       </c>
       <c r="AM5" t="n">
-        <v>6325</v>
+        <v>3575</v>
       </c>
       <c r="AN5" t="n">
-        <v>11500</v>
+        <v>6500</v>
       </c>
       <c r="AO5" t="n">
-        <v>17825</v>
+        <v>10075</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4400</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>12400</v>
       </c>
     </row>
     <row r="6">
@@ -2844,7 +2877,7 @@
         <v>7000</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>28000</v>
+        <v>28500</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>0</v>
@@ -2904,22 +2937,31 @@
         <v>1.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15400</v>
+        <v>15675</v>
       </c>
       <c r="AK6" t="n">
-        <v>28000</v>
+        <v>28500</v>
       </c>
       <c r="AL6" t="n">
-        <v>43400</v>
+        <v>44175</v>
       </c>
       <c r="AM6" t="n">
-        <v>6875</v>
+        <v>4675</v>
       </c>
       <c r="AN6" t="n">
-        <v>12500</v>
+        <v>8500</v>
       </c>
       <c r="AO6" t="n">
-        <v>19375</v>
+        <v>13175</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4950</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13950</v>
       </c>
     </row>
     <row r="7">
@@ -2973,7 +3015,7 @@
         <v>15000</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>45000</v>
+        <v>5000</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>0</v>
@@ -3033,22 +3075,31 @@
         <v>1.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24750</v>
+        <v>2750</v>
       </c>
       <c r="AK7" t="n">
-        <v>45000</v>
+        <v>5000</v>
       </c>
       <c r="AL7" t="n">
-        <v>69750</v>
+        <v>7750</v>
       </c>
       <c r="AM7" t="n">
-        <v>9900</v>
+        <v>2750</v>
       </c>
       <c r="AN7" t="n">
-        <v>18000</v>
+        <v>5000</v>
       </c>
       <c r="AO7" t="n">
-        <v>27900</v>
+        <v>7750</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3850</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10850</v>
       </c>
     </row>
   </sheetData>
